--- a/src/attributions/attributions_ig_traj_186.xlsx
+++ b/src/attributions/attributions_ig_traj_186.xlsx
@@ -1571,19 +1571,19 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3300717891832406</v>
+        <v>0.3827665924663091</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0715559603195321</v>
+        <v>0.06522246110835137</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2745683250917698</v>
+        <v>-0.2768355251572067</v>
       </c>
       <c r="G3" t="n">
         <v>-0</v>
@@ -1598,7 +1598,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1230731016746956</v>
+        <v>0.2064428623817476</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1607,13 +1607,13 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.01474076489099802</v>
+        <v>-0.0238456377067439</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.05538157913260666</v>
+        <v>-0.04474394118646838</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>-0</v>
@@ -1622,22 +1622,22 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.05059529695785629</v>
+        <v>-0.1153642001643249</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0844461271205503</v>
+        <v>-0.1191604085247303</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.01200920228547674</v>
+        <v>-0.1277442508830805</v>
       </c>
       <c r="Y3" t="n">
         <v>-0</v>
@@ -1649,22 +1649,22 @@
         <v>-0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.07484945483184587</v>
+        <v>0.132646163684042</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1206977934125089</v>
+        <v>0.0387695743690929</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.04866460691813951</v>
+        <v>0.1149006197518145</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
@@ -1673,67 +1673,67 @@
         <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.07119544544902322</v>
+        <v>0.1455013547618035</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.03811735484944442</v>
+        <v>-0.01374480761705609</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.1376088056272396</v>
+        <v>-0.2256212672572171</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.4130726967703659</v>
+        <v>0.6978190273283044</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.1443459722311549</v>
+        <v>-0.2697768455857925</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.4412848939116525</v>
+        <v>-0.3633048100662626</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.1506377607313553</v>
+        <v>0.1360536117962973</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1742,13 +1742,13 @@
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.05347675687943369</v>
+        <v>0.06053646996283717</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.1049832368429894</v>
+        <v>-0.1701248542315081</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
         <v>-0</v>
@@ -1757,52 +1757,52 @@
         <v>-0</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.001241521179766978</v>
+        <v>0.04129146176214286</v>
       </c>
       <c r="BN3" t="n">
         <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.04595569827406344</v>
+        <v>0.1163341047102528</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.004874259048764848</v>
+        <v>0.1439220101794011</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.1181577806685599</v>
+        <v>0.2540725767153242</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.1058184543848123</v>
+        <v>-0.09869266957400674</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.132063943881062</v>
+        <v>-0.2624447906176562</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB3" t="n">
         <v>-0</v>
@@ -1814,19 +1814,19 @@
         <v>-0</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.1418013593217869</v>
+        <v>-0.2838475265490725</v>
       </c>
       <c r="CF3" t="n">
         <v>0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.01988724322941855</v>
+        <v>-0.05482208513679845</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.1225837213827503</v>
+        <v>0.1768908909976367</v>
       </c>
       <c r="CJ3" t="n">
         <v>0</v>
@@ -1841,52 +1841,52 @@
         <v>0</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0.002577051405407591</v>
+        <v>-0.2961915192492241</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP3" t="n">
         <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.03955295125988306</v>
+        <v>0.06023581169610676</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.01071049945630149</v>
+        <v>0.1613290127276087</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0.1203442273119596</v>
+        <v>-0.2680537303245056</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.0008843008533723796</v>
+        <v>-0.04670032335655826</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.1376368356121673</v>
+        <v>0.1488019095165297</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD3" t="n">
         <v>0</v>
@@ -1895,73 +1895,73 @@
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.05035492395690995</v>
+        <v>-0.1127783666858438</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.03946517650984013</v>
+        <v>-0.06978145062611883</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.01075873510333086</v>
+        <v>0.1308242428626018</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.01694941608757988</v>
+        <v>-0.117000110414488</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.09948779961301946</v>
+        <v>-0.001251940370408</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0.01739172694419293</v>
+        <v>0.03954027789855375</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.08197198364690433</v>
+        <v>0.1398869355882332</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ3" t="n">
         <v>0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.02027926904204899</v>
+        <v>-0.03035784804289184</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.006968121358906684</v>
+        <v>0.1492745931554651</v>
       </c>
       <c r="EC3" t="n">
         <v>-0</v>
@@ -1973,22 +1973,22 @@
         <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.1589320542997175</v>
+        <v>-0.1295137576840679</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.009299724234294622</v>
+        <v>-0.075957590839193</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.1282868411446179</v>
+        <v>0.1612078610616276</v>
       </c>
       <c r="EL3" t="n">
         <v>-0</v>
@@ -2000,49 +2000,49 @@
         <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0.07048993694833507</v>
+        <v>-0.1745134722290684</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER3" t="n">
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.02324305345569702</v>
+        <v>-0.182689745252186</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.08760133249433456</v>
+        <v>0.2046257987955727</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.1250621501543555</v>
+        <v>-0.2613091677916803</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.01800593781749402</v>
+        <v>-0.1103268084619194</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.1259000268523936</v>
+        <v>0.1555532103102157</v>
       </c>
       <c r="FD3" t="n">
         <v>0</v>
@@ -2054,10 +2054,10 @@
         <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0.06363759334031313</v>
+        <v>-0.1504322189709761</v>
       </c>
       <c r="FI3" t="n">
         <v>0</v>
@@ -2066,73 +2066,73 @@
         <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.07296059240200616</v>
+        <v>-0.04250756222719893</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.1420996786131228</v>
+        <v>0.2620555431733647</v>
       </c>
       <c r="FM3" t="n">
         <v>0</v>
       </c>
       <c r="FN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO3" t="n">
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>-0.2030709208053865</v>
+        <v>-0.01945430781425148</v>
       </c>
       <c r="FR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS3" t="n">
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.03702473033228432</v>
+        <v>0.03164152151879818</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.09533563616206632</v>
+        <v>0.04735236813433847</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0.07011451616897375</v>
+        <v>-0.134003646650604</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0.05167880349454042</v>
+        <v>0.1331542078497562</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.06831910383453191</v>
+        <v>0.4384039956195732</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2718,25 +2718,25 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.009974763584958232</v>
+        <v>0.04538908935132382</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.02484827276060669</v>
+        <v>-0.1947707082608084</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02624043547660716</v>
+        <v>0.2513439976623449</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2745,40 +2745,40 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.006189820895266068</v>
+        <v>-0.0419055576159388</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.01860335630954559</v>
+        <v>-0.179775150367137</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002557930447763781</v>
+        <v>0.1825440131773233</v>
       </c>
       <c r="U5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.006635343022975433</v>
+        <v>-0.1326231924272519</v>
       </c>
       <c r="X5" t="n">
-        <v>0.00280216710336163</v>
+        <v>-0.02700077935624414</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
         <v>-0</v>
@@ -2790,73 +2790,73 @@
         <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.01394803877993088</v>
+        <v>0.02269550045015923</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.02259180929602682</v>
+        <v>-0.2778832793021365</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0006241881313132925</v>
+        <v>0.02513236962102311</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
         <v>-0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.003502043989700265</v>
+        <v>0.228786921313327</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.01114783438537903</v>
+        <v>0.1315506959575716</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.01730068416390367</v>
+        <v>-0.1540621430702762</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
         <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.0830733600823514</v>
+        <v>0.8956952660816797</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.003642930806783595</v>
+        <v>-0.1920154189571465</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.005465502619434911</v>
+        <v>-0.2095329064918507</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -2871,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.02921474241784109</v>
+        <v>-0.05076223510397743</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,40 +2880,40 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.01884703483625188</v>
+        <v>-0.09314335914194206</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.05016190856198541</v>
+        <v>-0.1289309439910103</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
         <v>-0</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.02959726640291917</v>
+        <v>0.05717839056177397</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.02778807925233992</v>
+        <v>0.1344999374153151</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.003547692415347169</v>
+        <v>0.1517300671884729</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,7 +2925,7 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.02889839929578373</v>
+        <v>0.4290051398469107</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
@@ -2934,43 +2934,43 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.004875607678371164</v>
+        <v>-0.007958140148571767</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.003972724829265086</v>
+        <v>-0.2626600987080719</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
         <v>-0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.01913912600836496</v>
+        <v>-0.2628866912740395</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
         <v>0</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.002135026085513022</v>
+        <v>-0.04390733275078211</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0191973431909024</v>
+        <v>0.1797208278592962</v>
       </c>
       <c r="CJ5" t="n">
         <v>0</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
         <v>0</v>
@@ -2979,157 +2979,157 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.007032614803363366</v>
+        <v>-0.2121162707226801</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
         <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.006061434769953307</v>
+        <v>0.09299239009770417</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.000731818718567445</v>
+        <v>0.0009462475321775621</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.01497062458752291</v>
+        <v>-0.238299787557628</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.002839177901422693</v>
+        <v>-0.04274363208764671</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.01854322392600371</v>
+        <v>0.1913888460343736</v>
       </c>
       <c r="DB5" t="n">
         <v>-0</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.00412168746430766</v>
+        <v>-0.05164177102471366</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH5" t="n">
         <v>-0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.01674462012801943</v>
+        <v>-0.1046624927010084</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.003772352168277471</v>
+        <v>0.03712806607285291</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.00554604599440869</v>
+        <v>-0.09242909978446429</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>-2.093883482958527e-05</v>
+        <v>0.002193784235796319</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.005960993096225278</v>
+        <v>-0.02036501438912705</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>-0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0176974282755442</v>
+        <v>0.07818231143801664</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.03087229249521856</v>
+        <v>-0.04593172216098722</v>
       </c>
       <c r="EB5" t="n">
-        <v>6.542452480773894e-05</v>
+        <v>0.1197872149082266</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.01504787102422738</v>
+        <v>-0.080699767320279</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
         <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.0007990531468292599</v>
+        <v>-0.1403731439581098</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.01143179878931843</v>
+        <v>0.0679282696626886</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
         <v>-0</v>
@@ -3138,10 +3138,10 @@
         <v>0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.01519073328862748</v>
+        <v>-0.1552889686109828</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
@@ -3150,52 +3150,52 @@
         <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.006855349999551023</v>
+        <v>-0.185037963554127</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.005903041009256044</v>
+        <v>0.04687577696272491</v>
       </c>
       <c r="EU5" t="n">
         <v>0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
         <v>0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.01728704629321368</v>
+        <v>-0.2659874299308909</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
         <v>0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.003339377789078943</v>
+        <v>-0.08316727539627608</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.02028736289821969</v>
+        <v>0.1591612669932086</v>
       </c>
       <c r="FD5" t="n">
         <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.0004674520848992576</v>
+        <v>-0.2346648057422885</v>
       </c>
       <c r="FI5" t="n">
         <v>0</v>
@@ -3204,25 +3204,25 @@
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.02510106216717171</v>
+        <v>0.05207123207672158</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.01948008075012654</v>
+        <v>0.2700689620411183</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.001677908513837637</v>
+        <v>-0.03035356408874377</v>
       </c>
       <c r="FR5" t="n">
         <v>-0</v>
@@ -3231,40 +3231,40 @@
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0004472156851491596</v>
+        <v>-0.002638939551354952</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.007819597312654736</v>
+        <v>0.1293249028959451</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.02765970628649874</v>
+        <v>-0.1303794041592252</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
         <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.005487899020820634</v>
+        <v>0.0926186146769131</v>
       </c>
       <c r="GE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF5" t="n">
         <v>0</v>
@@ -3278,22 +3278,22 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1192695503331691</v>
+        <v>0.4259240844977518</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.004982774638471177</v>
+        <v>0.02325259711149527</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.08608114004544752</v>
+        <v>-0.2357813871788519</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
         <v>-0</v>
@@ -3305,7 +3305,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05962128982855201</v>
+        <v>0.3020736418611836</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.003535902598285649</v>
+        <v>-0.04700047301443963</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.06312765184945848</v>
+        <v>-0.1871292576712967</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -3332,52 +3332,52 @@
         <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.004431461994426994</v>
+        <v>0.1440740692610349</v>
       </c>
       <c r="U6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.01296496711067889</v>
+        <v>-0.1473351965869563</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.005081038962445286</v>
+        <v>-0.02128206674656486</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.02188895936242346</v>
+        <v>0.09177809979474559</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.02406142852887019</v>
+        <v>-0.2881343925364444</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.0003753358165765185</v>
+        <v>-0.1172662198644401</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
@@ -3386,22 +3386,22 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.02069457914407428</v>
+        <v>0.2025058567965067</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.0004273440322982091</v>
+        <v>0.1138712563717369</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.03721583594612461</v>
+        <v>-0.1364594091371077</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
         <v>-0</v>
@@ -3410,22 +3410,22 @@
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.1258426774079187</v>
+        <v>0.7339104754674338</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.006908473540101982</v>
+        <v>-0.1954230750219034</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.08890924301077834</v>
+        <v>-0.2626690975176362</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -3434,13 +3434,13 @@
         <v>-0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC6" t="n">
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0587340061264499</v>
+        <v>-0.01243914821593659</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,40 +3449,40 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.03067984100595689</v>
+        <v>-0.08935147235246191</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.07072634723408817</v>
+        <v>-0.1891719239598585</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.05910564932944225</v>
+        <v>0.0609280269262114</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.02494336138433626</v>
+        <v>0.1100647208661755</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0.00180119999719473</v>
+        <v>0.05583373506679393</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>0</v>
@@ -3491,10 +3491,10 @@
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.04490659733770334</v>
+        <v>0.3571168955767911</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.001527363846823011</v>
+        <v>-0.06018561053082604</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.02697430343359734</v>
+        <v>-0.1711114828854337</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>-0</v>
@@ -3521,22 +3521,22 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.0319169106713487</v>
+        <v>-0.2469854321452575</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
         <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.001763986933781758</v>
+        <v>-0.02371025852815394</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.0358936002466208</v>
+        <v>0.1663637513113202</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
@@ -3548,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.006001989059289829</v>
+        <v>-0.2144639499679488</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
@@ -3557,64 +3557,64 @@
         <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.006744193826428356</v>
+        <v>0.1209775925889791</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.004978880749996592</v>
+        <v>0.02398997726088449</v>
       </c>
       <c r="CS6" t="n">
         <v>-0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.02431601008854693</v>
+        <v>-0.2235520882042806</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
         <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.003362219218195228</v>
+        <v>-0.03651660587776627</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.03547565415514608</v>
+        <v>0.1660380292472896</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
         <v>-0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.01199880622860433</v>
+        <v>-0.07208929714864197</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.005498104566310614</v>
+        <v>-0.05079464727650149</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.007104855500492164</v>
+        <v>-0.00184999396516972</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3623,31 +3623,31 @@
         <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.0208047224024852</v>
+        <v>-0.1010521737815442</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.01339464705080645</v>
+        <v>-0.0325141766650266</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.01277898081614594</v>
+        <v>0.0711807409532972</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
         <v>-0</v>
@@ -3656,19 +3656,19 @@
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.004350667914788425</v>
+        <v>0.04075960312369289</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.02354593776513374</v>
+        <v>0.1069817591457412</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.003223285706420582</v>
+        <v>0.09436576008219717</v>
       </c>
       <c r="EC6" t="n">
         <v>-0</v>
@@ -3677,13 +3677,13 @@
         <v>-0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
         <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.0146741718267519</v>
+        <v>-0.06448907104491809</v>
       </c>
       <c r="EH6" t="n">
         <v>0</v>
@@ -3692,79 +3692,79 @@
         <v>0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.001678417970468722</v>
+        <v>-0.08329975713285012</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.02735573020479543</v>
+        <v>0.07479002815229335</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN6" t="n">
         <v>0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.01782724179966334</v>
+        <v>-0.1204417764112646</v>
       </c>
       <c r="EQ6" t="n">
         <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.00870469510326298</v>
+        <v>-0.09566703187398093</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.02496973415082019</v>
+        <v>0.113458753860636</v>
       </c>
       <c r="EU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
         <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.02227044277997413</v>
+        <v>-0.2542825379077033</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA6" t="n">
         <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.001053424043881342</v>
+        <v>-0.05218010090534052</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.03617661906597879</v>
+        <v>0.1423791064533729</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
         <v>0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.01252046508404713</v>
+        <v>-0.2784378441396697</v>
       </c>
       <c r="FI6" t="n">
         <v>0</v>
@@ -3773,70 +3773,70 @@
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.02703584165179541</v>
+        <v>0.1313843581192732</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.02045161778165661</v>
+        <v>0.2624832739023138</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO6" t="n">
         <v>0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.00341873829493548</v>
+        <v>-0.04791751191951735</v>
       </c>
       <c r="FR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS6" t="n">
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.00179320043627667</v>
+        <v>0.002792798619521941</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.0283326344005647</v>
+        <v>0.1663757894560932</v>
       </c>
       <c r="FV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.02819657562732001</v>
+        <v>-0.06497788477635628</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
         <v>-0</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.01413429326605454</v>
+        <v>0.02622915352466389</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
         <v>0</v>
@@ -4416,154 +4416,154 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2470673339675286</v>
+        <v>0.5119102734620014</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.07107631889004938</v>
+        <v>-0.07459283593156114</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.06245754275723919</v>
+        <v>-0.02811411422245428</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.09227178167552343</v>
+        <v>-0.1226913887424731</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1667406778862869</v>
+        <v>0.5085404455387585</v>
       </c>
       <c r="L8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.06228561752228515</v>
+        <v>-0.1595161553284121</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.03925757719733591</v>
+        <v>-0.1044894789207739</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.06425434348144109</v>
+        <v>-0.06179721789400646</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.04862488334435178</v>
+        <v>0.1413421587672724</v>
       </c>
       <c r="U8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.01413004267081692</v>
+        <v>-0.1434690937105414</v>
       </c>
       <c r="W8" t="n">
-        <v>0.04084464383334924</v>
+        <v>-0.1418236495355908</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02532428950620072</v>
+        <v>-0.01251347641193619</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.01253982037823595</v>
+        <v>0.01572528633176841</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.04593867599148094</v>
+        <v>-0.2891957355881525</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.01574969571416014</v>
+        <v>-0.229704242835473</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.02241273800282759</v>
+        <v>-0.06558378510719831</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.0003858439164005091</v>
+        <v>0.2490723801463645</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.02732846244017635</v>
+        <v>-0.09101553964427603</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.01661321913402619</v>
+        <v>0.07410241254534554</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.03820053983764499</v>
+        <v>-0.1734804054902633</v>
       </c>
       <c r="AQ8" t="n">
         <v>-0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS8" t="n">
         <v>-0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.3233631004974464</v>
+        <v>0.7447966258471567</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0.01289951722344667</v>
+        <v>0.009627314842746112</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.04497915155305268</v>
+        <v>-0.298333832964767</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0354648694456766</v>
+        <v>-0.1552271123116166</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -4572,58 +4572,58 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0405671329837352</v>
+        <v>-0.07825980859227695</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.03952296273216901</v>
+        <v>-0.1506721154484284</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.08761817847448032</v>
+        <v>-0.07238187566313616</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.1341121543469001</v>
+        <v>-0.06384637555014611</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
         <v>-0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.06757601324394891</v>
+        <v>0.06307531946009515</v>
       </c>
       <c r="BN8" t="n">
         <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.04399398745384305</v>
+        <v>0.01000371463347163</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.07550316154742628</v>
+        <v>0.1449258821540388</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.01480205993569667</v>
+        <v>-0.003345793317380514</v>
       </c>
       <c r="BR8" t="n">
         <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT8" t="n">
         <v>0</v>
@@ -4632,49 +4632,49 @@
         <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.1144148588358406</v>
+        <v>0.3574906659729383</v>
       </c>
       <c r="BW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.02741738873750252</v>
+        <v>-0.0620348871789611</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.01228448887703824</v>
+        <v>-0.0889847889299286</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.02341035399114451</v>
+        <v>-0.1275410026604259</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.05962476350862466</v>
+        <v>-0.2301617720293408</v>
       </c>
       <c r="CF8" t="n">
         <v>-0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.004705178997843965</v>
+        <v>0.06410648263769868</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0005514138327993092</v>
+        <v>0.03724247445554827</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.04811097096076427</v>
+        <v>0.05456411145682984</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
@@ -4686,19 +4686,19 @@
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.0255097465537034</v>
+        <v>-0.1695260559268879</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>-0.03803183513895786</v>
+        <v>0.1333949391093027</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.03411626555440519</v>
+        <v>0.1376528156777883</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.0260685742945129</v>
+        <v>0.06983854618062595</v>
       </c>
       <c r="CS8" t="n">
         <v>0</v>
@@ -4707,85 +4707,85 @@
         <v>-0</v>
       </c>
       <c r="CU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.05150696782723785</v>
+        <v>-0.1991022902077415</v>
       </c>
       <c r="CX8" t="n">
         <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.02305801598471924</v>
+        <v>0.06765254579148221</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.005692642630525237</v>
+        <v>0.02125140835394585</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.05542675214326389</v>
+        <v>0.05673559716689788</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD8" t="n">
         <v>0</v>
       </c>
       <c r="DE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.01199060467535498</v>
+        <v>-0.03324187653436318</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.08295992851542498</v>
+        <v>0.0130642882253049</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0.01088382116913133</v>
+        <v>0.3131555434321701</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.005521887153297217</v>
+        <v>-0.003823724107825384</v>
       </c>
       <c r="DK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL8" t="n">
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.040410780575336</v>
+        <v>-0.1332702869746346</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.03242016509820098</v>
+        <v>0.0196641989568893</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.01984899235352522</v>
+        <v>-0.07445492767940215</v>
       </c>
       <c r="DS8" t="n">
-        <v>-0.01996661111591903</v>
+        <v>0.0737031063214427</v>
       </c>
       <c r="DT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
         <v>-0</v>
@@ -4794,190 +4794,190 @@
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.01388595666494536</v>
+        <v>0.147855382314605</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.001105128388854686</v>
+        <v>0.03502286539648919</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.0469621417259255</v>
+        <v>-0.06993763785523043</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.004174700878514094</v>
+        <v>-0.03764148773016745</v>
       </c>
       <c r="EC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.09296548194664334</v>
+        <v>-0.06865252182845862</v>
       </c>
       <c r="EH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.03680061152902687</v>
+        <v>0.08095844473853893</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0425160297853406</v>
+        <v>-0.001666582856452425</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.01771633204229689</v>
+        <v>0.008217359638360049</v>
       </c>
       <c r="EL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.03281044123292057</v>
+        <v>-0.07305494775873619</v>
       </c>
       <c r="EQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER8" t="n">
-        <v>-0.004028699809145656</v>
+        <v>-0.03024953573102541</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.002669262721220153</v>
+        <v>-0.03225420595340783</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.07442960411075553</v>
+        <v>0.1501144903331058</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
       </c>
       <c r="EW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.04773103287549313</v>
+        <v>-0.2468019469213336</v>
       </c>
       <c r="EZ8" t="n">
         <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.00481349260200125</v>
+        <v>0.06124521938781195</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.0188130287353303</v>
+        <v>0.01964466715465906</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.04687407699640002</v>
+        <v>0.03821392924890588</v>
       </c>
       <c r="FD8" t="n">
         <v>0</v>
       </c>
       <c r="FE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.04300894749619478</v>
+        <v>-0.1162440079991649</v>
       </c>
       <c r="FI8" t="n">
         <v>0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.0393158795368729</v>
+        <v>0.11500064642372</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.002415322640182559</v>
+        <v>0.03963205610838949</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.0148294699936243</v>
+        <v>0.1428247748803974</v>
       </c>
       <c r="FM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.0100187486740825</v>
+        <v>-0.1957695795711718</v>
       </c>
       <c r="FR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.00981322342514185</v>
+        <v>0.3013127627160383</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.00580302531620773</v>
+        <v>0.01143937384384452</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.002347975484260045</v>
+        <v>0.109223591063631</v>
       </c>
       <c r="FV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW8" t="n">
         <v>-0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.03034323131626698</v>
+        <v>-0.1448290485983767</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>-0.02736112547546804</v>
+        <v>-0.1006074055350331</v>
       </c>
       <c r="GC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.002133712833372655</v>
+        <v>-0.01937730013568087</v>
       </c>
       <c r="GE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5551,10 +5551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.6424650953820997</v>
+        <v>-0.238961158249</v>
       </c>
       <c r="C10" t="n">
         <v>-0</v>
@@ -5563,13 +5563,13 @@
         <v>-0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2685226564549291</v>
+        <v>-0.01621626532689649</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9193095657505658</v>
+        <v>0.215698691833053</v>
       </c>
       <c r="G10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5578,22 +5578,22 @@
         <v>-0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3521873768857793</v>
+        <v>-0.1642786857023738</v>
       </c>
       <c r="L10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>-0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0337381006801869</v>
+        <v>0.0539938408027779</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6317050480029249</v>
+        <v>0.1498192799456233</v>
       </c>
       <c r="P10" t="n">
         <v>-0</v>
@@ -5608,22 +5608,22 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.128445876908211</v>
+        <v>-0.09250741647785143</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
         <v>-0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1118856017212577</v>
+        <v>-0.005991025351602938</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.008831151732134468</v>
+        <v>-0.03397014972306713</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -5635,7 +5635,7 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.1997433967066109</v>
+        <v>0.05077835533231128</v>
       </c>
       <c r="AD10" t="n">
         <v>-0</v>
@@ -5644,10 +5644,10 @@
         <v>-0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0314248152168953</v>
+        <v>0.1557369139536982</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.1740990145579843</v>
+        <v>0.04800979965170532</v>
       </c>
       <c r="AH10" t="n">
         <v>-0</v>
@@ -5662,22 +5662,22 @@
         <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.128026019410889</v>
+        <v>-0.1144453559233114</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.09935156713526465</v>
+        <v>-0.07998475135721246</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.2666855287697762</v>
+        <v>0.1410559288515709</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -5686,10 +5686,10 @@
         <v>-0</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.398894292586535</v>
+        <v>-0.2968500868239511</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -5698,10 +5698,10 @@
         <v>-0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.4293323303842947</v>
+        <v>0.07489308395981019</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.8575942788005543</v>
+        <v>0.1189639219364783</v>
       </c>
       <c r="AZ10" t="n">
         <v>-0</v>
@@ -5710,13 +5710,13 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.3650158792477014</v>
+        <v>0.1025441145713944</v>
       </c>
       <c r="BE10" t="n">
         <v>-0</v>
@@ -5725,25 +5725,25 @@
         <v>-0</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.2350099665664009</v>
+        <v>0.2080913621062747</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.1705635004995789</v>
+        <v>0.1369969166126893</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>-0.1446220171567522</v>
+        <v>0.02878882107026522</v>
       </c>
       <c r="BN10" t="n">
         <v>0</v>
@@ -5752,13 +5752,13 @@
         <v>0</v>
       </c>
       <c r="BP10" t="n">
-        <v>-0.08195136223958766</v>
+        <v>-0.04368537745758733</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0.02346670112135132</v>
+        <v>-0.04467187405244637</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5770,22 +5770,22 @@
         <v>0</v>
       </c>
       <c r="BV10" t="n">
-        <v>-0.2426577409464317</v>
+        <v>-0.2184991790668978</v>
       </c>
       <c r="BW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX10" t="n">
         <v>-0</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.1056054733768832</v>
+        <v>-0.004271522980598305</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.3073572687405512</v>
+        <v>0.08513152425187674</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="n">
         <v>0</v>
@@ -5794,10 +5794,10 @@
         <v>-0</v>
       </c>
       <c r="CD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.1778754462370792</v>
+        <v>0.1255847658170457</v>
       </c>
       <c r="CF10" t="n">
         <v>0</v>
@@ -5806,40 +5806,40 @@
         <v>0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.03965049989464613</v>
+        <v>-0.01049187220397186</v>
       </c>
       <c r="CI10" t="n">
-        <v>-0.1785659787290148</v>
+        <v>-0.08320392431305056</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK10" t="n">
         <v>-0</v>
       </c>
       <c r="CL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM10" t="n">
         <v>-0</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.03458372351868977</v>
+        <v>0.08394446478923714</v>
       </c>
       <c r="CO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP10" t="n">
         <v>0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.2029424810957945</v>
+        <v>-0.1708271323030337</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.1026001211102127</v>
+        <v>-0.05864175839431174</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT10" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.1401937513139744</v>
+        <v>0.1194494801937152</v>
       </c>
       <c r="CX10" t="n">
         <v>-0</v>
@@ -5860,10 +5860,10 @@
         <v>-0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.08206863847373706</v>
+        <v>-0.005453496673305293</v>
       </c>
       <c r="DA10" t="n">
-        <v>-0.2176066497201161</v>
+        <v>-0.07868424703598739</v>
       </c>
       <c r="DB10" t="n">
         <v>-0</v>
@@ -5878,49 +5878,49 @@
         <v>-0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.01477233800790321</v>
+        <v>-0.003256450189991945</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
         <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.2480589590806219</v>
+        <v>0.06774831515585876</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.03364010339362548</v>
+        <v>-0.01200270045128158</v>
       </c>
       <c r="DK10" t="n">
         <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.08770862777594826</v>
+        <v>0.016784326646979</v>
       </c>
       <c r="DP10" t="n">
         <v>0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.1126888890027417</v>
+        <v>0.02639496560650748</v>
       </c>
       <c r="DS10" t="n">
-        <v>-0.08901216480912105</v>
+        <v>-0.02590312053084436</v>
       </c>
       <c r="DT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
@@ -5929,10 +5929,10 @@
         <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.1522823839599999</v>
+        <v>-0.005621351121560628</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
@@ -5941,10 +5941,10 @@
         <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.2801742088884288</v>
+        <v>0.03237888066052686</v>
       </c>
       <c r="EB10" t="n">
-        <v>-0.08890246743956863</v>
+        <v>0.01116584641356237</v>
       </c>
       <c r="EC10" t="n">
         <v>0</v>
@@ -5953,25 +5953,25 @@
         <v>-0</v>
       </c>
       <c r="EE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF10" t="n">
         <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.08209377798622129</v>
+        <v>0.06026917246943747</v>
       </c>
       <c r="EH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>-0.1762178285275917</v>
+        <v>0.005851109187019248</v>
       </c>
       <c r="EK10" t="n">
-        <v>-0.1605178813127047</v>
+        <v>-0.0122091824938285</v>
       </c>
       <c r="EL10" t="n">
         <v>0</v>
@@ -5980,40 +5980,40 @@
         <v>-0</v>
       </c>
       <c r="EN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.1108124016204603</v>
+        <v>0.1038414493790883</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.05478111683237148</v>
+        <v>0.07700131782067751</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.005404402937911741</v>
+        <v>0.1126644908508743</v>
       </c>
       <c r="EU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.1603310960978765</v>
+        <v>0.1345708743556027</v>
       </c>
       <c r="EZ10" t="n">
         <v>0</v>
@@ -6022,13 +6022,13 @@
         <v>0</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.07409387888034562</v>
+        <v>-0.00282445851945151</v>
       </c>
       <c r="FC10" t="n">
-        <v>-0.2201849284130288</v>
+        <v>-0.06679861431653838</v>
       </c>
       <c r="FD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE10" t="n">
         <v>-0</v>
@@ -6037,10 +6037,10 @@
         <v>0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.03473672545312253</v>
+        <v>0.1506127654110247</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
@@ -6049,37 +6049,37 @@
         <v>0</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.01399210106993324</v>
+        <v>-0.05028086661366655</v>
       </c>
       <c r="FL10" t="n">
-        <v>-0.2096025653999178</v>
+        <v>-0.09382152697030378</v>
       </c>
       <c r="FM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN10" t="n">
         <v>-0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.02668543205346089</v>
+        <v>0.1268773200606509</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
         <v>0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.1264584963120524</v>
+        <v>-0.003303276351113327</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0.2822381290090588</v>
+        <v>-0.08288601663707666</v>
       </c>
       <c r="FV10" t="n">
         <v>0</v>
@@ -6091,13 +6091,13 @@
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.09953370577319758</v>
+        <v>0.09520569439790905</v>
       </c>
       <c r="GA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB10" t="n">
         <v>0</v>
@@ -6106,7 +6106,7 @@
         <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.1004528293090282</v>
+        <v>0.01819785778274406</v>
       </c>
       <c r="GE10" t="n">
         <v>0</v>
@@ -6120,22 +6120,22 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1502369360554782</v>
+        <v>0.491767413737112</v>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.008927514244529059</v>
+        <v>-0.009709867113094241</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.09888545409318301</v>
+        <v>-0.2431786965210316</v>
       </c>
       <c r="G11" t="n">
         <v>-0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1271304598174303</v>
+        <v>0.6316525952191819</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,16 +6159,16 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.01089835202521372</v>
+        <v>-0.1392843353914876</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0783768492877772</v>
+        <v>-0.1982767980040329</v>
       </c>
       <c r="P11" t="n">
         <v>-0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>-0</v>
@@ -6177,7 +6177,7 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01406664933599338</v>
+        <v>0.1250903903244557</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
@@ -6186,16 +6186,16 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.01163174034852721</v>
+        <v>-0.0003448818803299358</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.01608143367400639</v>
+        <v>-0.1052833383147869</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -6204,19 +6204,19 @@
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.01815333265299036</v>
+        <v>0.008375186205488605</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.01138731084383792</v>
+        <v>-0.07011827411587897</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.01283653694787572</v>
+        <v>0.05571839476122591</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -6231,22 +6231,22 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.009658263572920947</v>
+        <v>0.1422156905207082</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.01273304547668335</v>
+        <v>0.06460569189677982</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.04548744823212662</v>
+        <v>-0.07999960663684222</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6255,22 +6255,22 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1131099322282011</v>
+        <v>0.6587008043839068</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.008046682939665597</v>
+        <v>-0.2522304522874511</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.06413723359496366</v>
+        <v>-0.2714495943249056</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -6279,13 +6279,13 @@
         <v>-0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.06271761649903757</v>
+        <v>-0.1746781606573581</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,10 +6294,10 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.02778144072014075</v>
+        <v>0.003790200711980096</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.05478981845657747</v>
+        <v>-0.02423411462128557</v>
       </c>
       <c r="BI11" t="n">
         <v>-0</v>
@@ -6306,52 +6306,52 @@
         <v>0</v>
       </c>
       <c r="BK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.04508534483846972</v>
+        <v>-0.001607280047622419</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.01655350643874781</v>
+        <v>0.07419388358712171</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.02159309678048069</v>
+        <v>0.03211741077777853</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.06194934326115653</v>
+        <v>0.4001682158251685</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.00682530481898205</v>
+        <v>-0.0268493771319939</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.02522235716318174</v>
+        <v>-0.138401433707689</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
@@ -6366,25 +6366,25 @@
         <v>0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.03100320747669416</v>
+        <v>-0.2141630117101869</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.003749707790733271</v>
+        <v>0.02322062994529397</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.02417479103891857</v>
+        <v>0.0862227776316654</v>
       </c>
       <c r="CJ11" t="n">
         <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL11" t="n">
         <v>0</v>
@@ -6393,61 +6393,61 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.01509788203104848</v>
+        <v>-0.09481783950663464</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.007723560738313585</v>
+        <v>0.08183779708420305</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.009780753569641436</v>
+        <v>0.03933531447453385</v>
       </c>
       <c r="CS11" t="n">
         <v>-0</v>
       </c>
       <c r="CT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
         <v>-0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.02239171009081182</v>
+        <v>-0.2019946592039993</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.002863624483164992</v>
+        <v>0.01488198229285261</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.02814939522108042</v>
+        <v>0.1020558446508183</v>
       </c>
       <c r="DB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.003836478699838737</v>
+        <v>0.009536439045192248</v>
       </c>
       <c r="DG11" t="n">
         <v>0</v>
@@ -6456,10 +6456,10 @@
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.004091967992340899</v>
+        <v>0.01593646258162737</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.01397420832442544</v>
+        <v>0.07189957042075333</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6471,28 +6471,28 @@
         <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.01704503677658079</v>
+        <v>-0.0696898762971544</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.003286574396261566</v>
+        <v>-0.01823300728046297</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.007142852024274416</v>
+        <v>0.07740230647602303</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
         <v>0</v>
@@ -6501,46 +6501,46 @@
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.03198524904296758</v>
+        <v>-0.1316260421402424</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.009290396532285415</v>
+        <v>0.06863147766280282</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.01965276513794352</v>
+        <v>-0.09547324932019342</v>
       </c>
       <c r="EC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
         <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.01623919462095659</v>
+        <v>-0.1198386945516544</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.004379925354965506</v>
+        <v>-0.04560696921898525</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.01378226225774321</v>
+        <v>0.026394224658826</v>
       </c>
       <c r="EL11" t="n">
         <v>-0</v>
@@ -6555,19 +6555,19 @@
         <v>0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.006708912287874588</v>
+        <v>0.08951748017971926</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.007923084315139784</v>
+        <v>0.0114732179245419</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.001073093312886728</v>
+        <v>-0.03983245381944273</v>
       </c>
       <c r="EU11" t="n">
         <v>0</v>
@@ -6576,52 +6576,52 @@
         <v>0</v>
       </c>
       <c r="EW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX11" t="n">
         <v>0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.02328791796884555</v>
+        <v>-0.2335535756294134</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.001756391519732766</v>
+        <v>0.001239501381015964</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.03015991412076431</v>
+        <v>0.1011557440820771</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-4.77257699472737e-05</v>
+        <v>-0.1174067069753251</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.01958520368550817</v>
+        <v>-0.01281575562559527</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.03015035715780252</v>
+        <v>0.1037807413401616</v>
       </c>
       <c r="FM11" t="n">
         <v>-0</v>
@@ -6636,7 +6636,7 @@
         <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.0140895826239611</v>
+        <v>-0.2145251297919641</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
@@ -6645,37 +6645,37 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.0262240450447144</v>
+        <v>-0.04756804326272752</v>
       </c>
       <c r="FU11" t="n">
-        <v>-0.001126322255501285</v>
+        <v>-0.007928796056339945</v>
       </c>
       <c r="FV11" t="n">
         <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
         <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.01820012985231997</v>
+        <v>-0.1029856525690179</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.03639466012705586</v>
+        <v>0.05113667331309434</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6684,7 +6684,7 @@
         <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,16 +6692,16 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.3601578982504174</v>
+        <v>-0.4782815955224255</v>
       </c>
       <c r="C12" t="n">
         <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2033179747801306</v>
+        <v>0.1435215279772306</v>
       </c>
       <c r="E12" t="n">
-        <v>0.229711924151425</v>
+        <v>0.0895994081987538</v>
       </c>
       <c r="F12" t="n">
         <v>-0</v>
@@ -6713,25 +6713,25 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3079370323486188</v>
+        <v>-0.6273752135586758</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2301396272357279</v>
+        <v>0.2950827062286282</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2602756491309543</v>
+        <v>0.1967318583408129</v>
       </c>
       <c r="O12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -6746,25 +6746,25 @@
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.09719281926230197</v>
+        <v>-0.06817523078245118</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.01366808264582559</v>
+        <v>0.01684148636256588</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.05190674432563599</v>
+        <v>-0.008996871032175932</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>-0</v>
@@ -6773,43 +6773,43 @@
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.1558473339717582</v>
+        <v>-0.03830504311207556</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.04539164880464687</v>
+        <v>0.1667803674149911</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.03613701508554003</v>
+        <v>-0.262483150316759</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.04440189730239632</v>
+        <v>-0.1774589574907677</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.03348037937026407</v>
+        <v>0.05165517057107236</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.05712653909328923</v>
+        <v>-0.2916620396914731</v>
       </c>
       <c r="AP12" t="n">
         <v>-0</v>
@@ -6821,58 +6821,58 @@
         <v>-0</v>
       </c>
       <c r="AS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0.2664756077292114</v>
+        <v>-0.283628566268589</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.02375911508934116</v>
+        <v>0.1818948375101984</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.01629993587220517</v>
+        <v>0.04616690612004751</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.007178569004002106</v>
+        <v>0.05660104569558545</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.1949730473314907</v>
+        <v>-0.005530514363629451</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.2682629267318988</v>
+        <v>0.1588687063281517</v>
       </c>
       <c r="BH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI12" t="n">
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK12" t="n">
         <v>-0</v>
@@ -6881,16 +6881,16 @@
         <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>-0.09829628806691544</v>
+        <v>0.1581041006799179</v>
       </c>
       <c r="BN12" t="n">
         <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>-0.02423852839052141</v>
+        <v>0.1079810587582977</v>
       </c>
       <c r="BP12" t="n">
-        <v>-0.09607142166094602</v>
+        <v>0.002044237755174478</v>
       </c>
       <c r="BQ12" t="n">
         <v>0</v>
@@ -6908,25 +6908,25 @@
         <v>0</v>
       </c>
       <c r="BV12" t="n">
-        <v>-0.2074385373447977</v>
+        <v>-0.2182235551507777</v>
       </c>
       <c r="BW12" t="n">
         <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.003980807508366734</v>
+        <v>0.0849635451486782</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.04618738944653349</v>
+        <v>0.00229788063085726</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA12" t="n">
         <v>0</v>
       </c>
       <c r="CB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC12" t="n">
         <v>-0</v>
@@ -6935,16 +6935,16 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.084919599878391</v>
+        <v>0.2413504394086344</v>
       </c>
       <c r="CF12" t="n">
         <v>0</v>
       </c>
       <c r="CG12" t="n">
-        <v>-0.04658422953175845</v>
+        <v>-0.07373545075727592</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.006309169201297392</v>
+        <v>-0.0005468613986733546</v>
       </c>
       <c r="CI12" t="n">
         <v>0</v>
@@ -6962,19 +6962,19 @@
         <v>-0</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.029695994560285</v>
+        <v>0.1161385091020462</v>
       </c>
       <c r="CO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.07528839507227683</v>
+        <v>-0.137058259138777</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.08070675357246687</v>
+        <v>-0.0854847128518456</v>
       </c>
       <c r="CR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS12" t="n">
         <v>0</v>
@@ -6989,22 +6989,22 @@
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.07693777221437838</v>
+        <v>0.2516131352312672</v>
       </c>
       <c r="CX12" t="n">
         <v>-0</v>
       </c>
       <c r="CY12" t="n">
-        <v>-0.06177501692314585</v>
+        <v>-0.07618181200368075</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.01336734236537262</v>
+        <v>-0.03214622703501956</v>
       </c>
       <c r="DA12" t="n">
         <v>-0</v>
       </c>
       <c r="DB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC12" t="n">
         <v>-0</v>
@@ -7016,19 +7016,19 @@
         <v>-0</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.1532591449652622</v>
+        <v>0.1741365253411854</v>
       </c>
       <c r="DG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0.05279723234694482</v>
+        <v>-0.02630469104044088</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0.006707620845180614</v>
+        <v>-0.0006343040407488659</v>
       </c>
       <c r="DJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK12" t="n">
         <v>0</v>
@@ -7037,22 +7037,22 @@
         <v>-0</v>
       </c>
       <c r="DM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.05357204664258596</v>
+        <v>0.09582967514791894</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.0330964648968045</v>
+        <v>-0.06340978073097117</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.06470831587381612</v>
+        <v>0.04255529446039405</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -7070,25 +7070,25 @@
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.07122573255063062</v>
+        <v>0.04441902928564788</v>
       </c>
       <c r="DY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.06984165891264819</v>
+        <v>0.07031645217848789</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.04246859005333956</v>
+        <v>-0.0198557432065995</v>
       </c>
       <c r="EB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE12" t="n">
         <v>0</v>
@@ -7097,22 +7097,22 @@
         <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.0535041488041897</v>
+        <v>0.2824157268337482</v>
       </c>
       <c r="EH12" t="n">
         <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>-0.04058853519054895</v>
+        <v>-0.0499538331469043</v>
       </c>
       <c r="EJ12" t="n">
-        <v>-0.1002015722578072</v>
+        <v>-0.04865882304719942</v>
       </c>
       <c r="EK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM12" t="n">
         <v>0</v>
@@ -7121,22 +7121,22 @@
         <v>0</v>
       </c>
       <c r="EO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.007120255844943923</v>
+        <v>-0.1707167129853674</v>
       </c>
       <c r="EQ12" t="n">
         <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.02705471471589081</v>
+        <v>-0.03567192987989543</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.03437756331861797</v>
+        <v>0.01440081166870209</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
         <v>-0</v>
@@ -7151,16 +7151,16 @@
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.07849812929132242</v>
+        <v>0.2807194931226091</v>
       </c>
       <c r="EZ12" t="n">
         <v>0</v>
       </c>
       <c r="FA12" t="n">
-        <v>-0.05811437554401102</v>
+        <v>-0.09250071840641259</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.01236194499351699</v>
+        <v>-0.0004398324501113159</v>
       </c>
       <c r="FC12" t="n">
         <v>0</v>
@@ -7169,91 +7169,91 @@
         <v>-0</v>
       </c>
       <c r="FE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG12" t="n">
         <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.06071708026847682</v>
+        <v>0.1058673328357576</v>
       </c>
       <c r="FI12" t="n">
         <v>0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.09577750444394238</v>
+        <v>0.1335995164212805</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.05169213152623511</v>
+        <v>0.08330987196921266</v>
       </c>
       <c r="FL12" t="n">
         <v>0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.01664277309480622</v>
+        <v>0.2197885685123973</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.03111925298530424</v>
+        <v>0.008441848319834015</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.01785872423868011</v>
+        <v>-0.07024281221436443</v>
       </c>
       <c r="FU12" t="n">
         <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX12" t="n">
         <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.04758904338844063</v>
+        <v>0.226356842976614</v>
       </c>
       <c r="GA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.06828406747529107</v>
+        <v>-0.0002259311968922013</v>
       </c>
       <c r="GC12" t="n">
         <v>-0</v>
       </c>
       <c r="GD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE12" t="n">
         <v>0</v>
       </c>
       <c r="GF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5792437066328294</v>
+        <v>0.3563346611196312</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,16 +7270,16 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1274810186006819</v>
+        <v>-0.03092164831917627</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5091105243607013</v>
+        <v>-0.1426984252606821</v>
       </c>
       <c r="G13" t="n">
         <v>-0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -7288,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5760069712492182</v>
+        <v>0.5036583725829984</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,25 +7297,25 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.05813319017185963</v>
+        <v>-0.1219332840142775</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5537183048372705</v>
+        <v>-0.2176796523836552</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.04755236829990615</v>
+        <v>0.1064887658080962</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -7324,37 +7324,37 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.110654745010335</v>
+        <v>-0.1166618233662825</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.02565384337818499</v>
+        <v>-0.005090410387975141</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.0275390229202471</v>
+        <v>-0.02931597959110936</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.0215953269672738</v>
+        <v>-0.2716371709374638</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.04212379964103503</v>
+        <v>-0.004549947446162852</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7369,7 +7369,7 @@
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.09769455732862328</v>
+        <v>0.03627142449193518</v>
       </c>
       <c r="AM13" t="n">
         <v>-0</v>
@@ -7378,10 +7378,10 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0006567358219328438</v>
+        <v>-0.03902280683020567</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.09125932246545443</v>
+        <v>0.0179704578611553</v>
       </c>
       <c r="AQ13" t="n">
         <v>-0</v>
@@ -7393,10 +7393,10 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.4681216858609668</v>
+        <v>0.4830067608289389</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
@@ -7405,16 +7405,16 @@
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.07547865179868263</v>
+        <v>-0.2471306261364534</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.2411337016768416</v>
+        <v>-0.1030859309087518</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>0</v>
@@ -7423,7 +7423,7 @@
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.1256404465667237</v>
+        <v>-0.02640743229741034</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,52 +7432,52 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.1561352566964735</v>
+        <v>-0.01826023118805718</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.2061257706689008</v>
+        <v>-0.08055430902221697</v>
       </c>
       <c r="BI13" t="n">
         <v>-0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1601394364002145</v>
+        <v>0.05420754045649814</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>-0.001140776253103799</v>
+        <v>0.07284421821868936</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.01590004500465311</v>
+        <v>-0.03856732649621976</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.2485805446403976</v>
+        <v>0.2599856884467435</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
@@ -7486,10 +7486,10 @@
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.07451044470466224</v>
+        <v>-0.07364203894135758</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.1461459617618215</v>
+        <v>-0.09421125771368159</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7498,28 +7498,28 @@
         <v>-0</v>
       </c>
       <c r="CC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD13" t="n">
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.09586491076524317</v>
+        <v>-0.1098733076809664</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.006446215008329582</v>
+        <v>0.02944543385110552</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.1165299558341483</v>
+        <v>0.04753346200453771</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
@@ -7531,100 +7531,100 @@
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.003115304557728661</v>
+        <v>-0.132883428025923</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.01787048106919314</v>
+        <v>0.1103401426896391</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.02395170569775671</v>
+        <v>0.1006350723349099</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.07769714451202178</v>
+        <v>-0.1101429362917546</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.005546675415865648</v>
+        <v>0.008845732805488119</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.121821495728354</v>
+        <v>0.06877497437296268</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
         <v>-0</v>
       </c>
       <c r="DD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.04474311101682561</v>
+        <v>-0.04971666937476797</v>
       </c>
       <c r="DG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.05347417951927155</v>
+        <v>-0.168019676363107</v>
       </c>
       <c r="DJ13" t="n">
-        <v>-0.001451015452034701</v>
+        <v>0.04964933054648572</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM13" t="n">
         <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.003472330483317901</v>
+        <v>-0.01092191807312633</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.03362394520549131</v>
+        <v>-0.05045557676934236</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.007595696074924218</v>
+        <v>0.06265048639325359</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
@@ -7633,13 +7633,13 @@
         <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.06633790709106792</v>
+        <v>-0.02029626083507293</v>
       </c>
       <c r="DY13" t="n">
         <v>0</v>
@@ -7648,25 +7648,25 @@
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.02092571729254978</v>
+        <v>-0.07606006179769176</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.0604119105792296</v>
+        <v>0.02755687738840463</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
         <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.108232070485527</v>
+        <v>-0.04202635601058043</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
@@ -7675,79 +7675,79 @@
         <v>-0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.02331439806358535</v>
+        <v>0.02215210337803252</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.1265440928468862</v>
+        <v>-0.009410661920081128</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
         <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.03263884978846953</v>
+        <v>-0.01312609594229622</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.0146199236652245</v>
+        <v>-0.01706506412837016</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.07942412872194721</v>
+        <v>0.1215373664251312</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.07440339027998528</v>
+        <v>-0.1296503996940592</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.005603887711857129</v>
+        <v>0.000249308693892745</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.1105132503528639</v>
+        <v>0.03831841965707554</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.003945683446421438</v>
+        <v>0.1922076591772191</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
@@ -7756,16 +7756,16 @@
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.0100714325585216</v>
+        <v>-0.09426401307233671</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.05596894958747622</v>
+        <v>0.109675009652774</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
         <v>0</v>
@@ -7774,46 +7774,46 @@
         <v>0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.005437178968010783</v>
+        <v>0.009855611703085876</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.009291071496026496</v>
+        <v>-0.0251904100577068</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.03707465793457311</v>
+        <v>-0.05046906775903426</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.05130643391850202</v>
+        <v>-0.03420563764413689</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.05910585980061403</v>
+        <v>0.05732790399884384</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
@@ -7822,7 +7822,7 @@
         <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -8968,7 +8968,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1544188935148341</v>
+        <v>0.3958643794029042</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -8977,25 +8977,25 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.07434624519471678</v>
+        <v>-0.02084509152020293</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.07191094627322574</v>
+        <v>-0.1446385525758582</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H16" t="n">
         <v>-0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1313128974087503</v>
+        <v>0.4986440986933964</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -9004,25 +9004,25 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.05300828472760943</v>
+        <v>-0.1279690718404325</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.07991690897304321</v>
+        <v>-0.2041604031644494</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.01285498906148165</v>
+        <v>0.08982252365081479</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -9031,40 +9031,40 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.009143915894461702</v>
+        <v>-0.0746323075620289</v>
       </c>
       <c r="X16" t="n">
-        <v>0.008585893434490358</v>
+        <v>-0.009302112134788276</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.00708099261352923</v>
+        <v>-0.03024932641232912</v>
       </c>
       <c r="AD16" t="n">
         <v>-0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.01095058767563661</v>
+        <v>-0.2307873373409146</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.008891241431807639</v>
+        <v>0.01709925190226669</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI16" t="n">
         <v>-0</v>
@@ -9076,22 +9076,22 @@
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.009017842687066626</v>
+        <v>0.04035664814959713</v>
       </c>
       <c r="AM16" t="n">
         <v>-0</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.008681091507523003</v>
+        <v>-0.02778306521480335</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.01371395358608961</v>
+        <v>-0.0001885847210065052</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
         <v>-0</v>
@@ -9100,25 +9100,25 @@
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.09654125682359209</v>
+        <v>0.3938336471289925</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
       </c>
       <c r="AW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.02558823624540049</v>
+        <v>-0.2563008768056509</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.01930057289415121</v>
+        <v>-0.1024042275531773</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA16" t="n">
         <v>-0</v>
@@ -9130,7 +9130,7 @@
         <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.0302820312550028</v>
+        <v>0.00252955785861262</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
@@ -9139,52 +9139,52 @@
         <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.04866486776021819</v>
+        <v>-0.002904869744809502</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.0543366550675645</v>
+        <v>-0.04804601829997016</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
         <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.03448809281252849</v>
+        <v>0.03959616992019722</v>
       </c>
       <c r="BN16" t="n">
         <v>-0</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.01721900225294691</v>
+        <v>0.04865757265505019</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.01589760666920734</v>
+        <v>-0.02422771510152101</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
         <v>-0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.04605661846881794</v>
+        <v>0.2209306048771014</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
@@ -9193,10 +9193,10 @@
         <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.01045136467074858</v>
+        <v>-0.05304717578285637</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0.01144505830400866</v>
+        <v>-0.09802608447146666</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
@@ -9208,28 +9208,28 @@
         <v>-0</v>
       </c>
       <c r="CD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.02315840521840748</v>
+        <v>-0.1034167076342855</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
         <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.006584241803874971</v>
+        <v>0.02809609202439048</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.01672923858127688</v>
+        <v>0.05187316016624946</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL16" t="n">
         <v>0</v>
@@ -9238,76 +9238,76 @@
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.001485202031397698</v>
+        <v>-0.1324474891003564</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
       </c>
       <c r="CP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.0073279866417078</v>
+        <v>0.1474936523834096</v>
       </c>
       <c r="CR16" t="n">
-        <v>-0.01263667932660277</v>
+        <v>0.06768225135802683</v>
       </c>
       <c r="CS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV16" t="n">
         <v>-0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.01765724039905513</v>
+        <v>-0.1010686269832201</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.005379815246833458</v>
+        <v>0.015331665117897</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.01733536584598776</v>
+        <v>0.07164908613476234</v>
       </c>
       <c r="DB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.0301532257095577</v>
+        <v>-0.08033913368697386</v>
       </c>
       <c r="DG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.04821482242880116</v>
+        <v>-0.1956340256185488</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.01088256427121481</v>
+        <v>0.06007360194547549</v>
       </c>
       <c r="DK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL16" t="n">
         <v>-0</v>
@@ -9316,79 +9316,79 @@
         <v>0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.005855340341051488</v>
+        <v>-0.01837878589909518</v>
       </c>
       <c r="DP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ16" t="n">
         <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.02068669027473315</v>
+        <v>-0.03498485093664613</v>
       </c>
       <c r="DS16" t="n">
-        <v>-0.007959741920477664</v>
+        <v>0.02766281593663096</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW16" t="n">
         <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.02656132921347498</v>
+        <v>-0.006562249680281331</v>
       </c>
       <c r="DY16" t="n">
         <v>0</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.01415902346671893</v>
+        <v>-0.06639004196760329</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.01832937144328398</v>
+        <v>0.0166167110461417</v>
       </c>
       <c r="EC16" t="n">
         <v>-0</v>
       </c>
       <c r="ED16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.02815144169986555</v>
+        <v>-0.04669363257947479</v>
       </c>
       <c r="EH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.006443556042594025</v>
+        <v>0.01152574949112689</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.01244994054135613</v>
+        <v>0.004292513796186449</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
         <v>-0</v>
@@ -9400,79 +9400,79 @@
         <v>0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.009990529301953644</v>
+        <v>-0.04251452547465764</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.002515272087712165</v>
+        <v>-0.0155457864232985</v>
       </c>
       <c r="ET16" t="n">
-        <v>-0.009720591527442599</v>
+        <v>0.0860015087308605</v>
       </c>
       <c r="EU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV16" t="n">
         <v>0</v>
       </c>
       <c r="EW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.01816137902611428</v>
+        <v>-0.1214162651914464</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.008609350245061197</v>
+        <v>0.002555874606952007</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.0205748469995555</v>
+        <v>0.04479780620918175</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG16" t="n">
         <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.01363540422291733</v>
+        <v>0.1511574967464079</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ16" t="n">
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.01161635186728579</v>
+        <v>-0.08862515265782175</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.01895218087121359</v>
+        <v>0.109636536573462</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
         <v>0</v>
@@ -9481,55 +9481,55 @@
         <v>0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>6.383140881813266e-05</v>
+        <v>0.00150547842735951</v>
       </c>
       <c r="FR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS16" t="n">
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.001260441709090497</v>
+        <v>-0.009248608646502012</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.01957513267543856</v>
+        <v>-0.0243058301229967</v>
       </c>
       <c r="FV16" t="n">
         <v>0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.003079416305427231</v>
+        <v>-0.02878331499979738</v>
       </c>
       <c r="GA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB16" t="n">
         <v>-0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0.0048316269926084</v>
+        <v>0.0646616299022493</v>
       </c>
       <c r="GE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF16" t="n">
         <v>-0</v>
       </c>
       <c r="GG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
